--- a/Source Data/Tagging/Tag Returns/Tag Returns spreadsheets/Connors Fish Tag Data 2024.xlsx
+++ b/Source Data/Tagging/Tag Returns/Tag Returns spreadsheets/Connors Fish Tag Data 2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://herringscience.sharepoint.com/sites/AFF44Contract/Shared Documents/Website/2024 Returns/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\herri\Documents\GitHub\HerringScience.github.io\Source Data\Tagging\Tag Returns\Tag Returns spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1365" documentId="8_{DE61676B-7AED-41C5-BBCE-5889CDA554D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AB7EDF1-569F-46E3-885C-8C88D9DA41A4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1713307A-5635-4F11-ACB9-C45EBD605196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="hidden" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2024" sheetId="8" r:id="rId1"/>
@@ -4232,6 +4232,12 @@
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="15" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4239,12 +4245,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4552,30 +4552,30 @@
     <col min="1" max="1" width="15.140625" style="39" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" style="39" customWidth="1"/>
     <col min="3" max="3" width="24.7109375" style="39" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="39" customWidth="1"/>
-    <col min="5" max="5" width="28.42578125" style="39" customWidth="1"/>
-    <col min="6" max="6" width="48" style="39" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="39" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" style="39" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="28.42578125" style="39" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="48" style="39" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="39" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="23" style="39" customWidth="1"/>
-    <col min="9" max="9" width="17.140625" style="39" customWidth="1"/>
-    <col min="10" max="10" width="22.140625" style="39" customWidth="1"/>
-    <col min="11" max="11" width="28" style="39" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" style="39" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="22.140625" style="39" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="28" style="39" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="63" t="s">
         <v>1002</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="60" t="s">
@@ -9086,19 +9086,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="65" t="s">
         <v>587</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="65"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="67"/>
     </row>
     <row r="2" spans="1:11" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="45" t="s">
@@ -30596,15 +30596,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="aa15ca5b-4450-4fec-8212-75ae51eef6c9">
@@ -30613,6 +30604,15 @@
     <TaxCatchAll xmlns="9b77705d-b477-4602-ae15-a5316c12e631" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -30635,14 +30635,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23B4CB3F-45FF-4904-B891-7C75FD7D91ED}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77043088-EBE2-4231-BB0C-EDD565434295}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -30651,4 +30643,12 @@
     <ds:schemaRef ds:uri="9b77705d-b477-4602-ae15-a5316c12e631"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23B4CB3F-45FF-4904-B891-7C75FD7D91ED}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Source Data/Tagging/Tag Returns/Tag Returns spreadsheets/Connors Fish Tag Data 2024.xlsx
+++ b/Source Data/Tagging/Tag Returns/Tag Returns spreadsheets/Connors Fish Tag Data 2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\herri\Documents\GitHub\HerringScience.github.io\Source Data\Tagging\Tag Returns\Tag Returns spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1713307A-5635-4F11-ACB9-C45EBD605196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9A561D-6781-462B-96A3-A8C2553B8B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="hidden" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2025" yWindow="2550" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2024" sheetId="8" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5805" uniqueCount="1216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5805" uniqueCount="1217">
   <si>
     <t>DATE</t>
   </si>
@@ -3687,6 +3687,9 @@
   </si>
   <si>
     <t>65 02.9</t>
+  </si>
+  <si>
+    <t>300823 - Comeaus</t>
   </si>
 </sst>
 </file>
@@ -4552,10 +4555,10 @@
     <col min="1" max="1" width="15.140625" style="39" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" style="39" customWidth="1"/>
     <col min="3" max="3" width="24.7109375" style="39" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="39" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="28.42578125" style="39" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="48" style="39" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="39" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" style="39" customWidth="1"/>
+    <col min="5" max="5" width="28.42578125" style="39" customWidth="1"/>
+    <col min="6" max="6" width="48" style="39" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="39" customWidth="1"/>
     <col min="8" max="8" width="23" style="39" customWidth="1"/>
     <col min="9" max="9" width="17.140625" style="39" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="22.140625" style="39" hidden="1" customWidth="1"/>
@@ -7663,7 +7666,7 @@
         <v>593</v>
       </c>
       <c r="L104" t="s">
-        <v>1143</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -7686,7 +7689,7 @@
         <v>593</v>
       </c>
       <c r="L105" t="s">
-        <v>1143</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -30596,6 +30599,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="aa15ca5b-4450-4fec-8212-75ae51eef6c9">
@@ -30604,15 +30616,6 @@
     <TaxCatchAll xmlns="9b77705d-b477-4602-ae15-a5316c12e631" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -30635,6 +30638,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23B4CB3F-45FF-4904-B891-7C75FD7D91ED}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77043088-EBE2-4231-BB0C-EDD565434295}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -30643,12 +30654,4 @@
     <ds:schemaRef ds:uri="9b77705d-b477-4602-ae15-a5316c12e631"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23B4CB3F-45FF-4904-B891-7C75FD7D91ED}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>